--- a/result1.xlsx
+++ b/result1.xlsx
@@ -8,6 +8,7 @@
   <sheets>
     <sheet name="计划购电量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="充放电量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="对照实验" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1864,7 +1865,7 @@
         </is>
       </c>
       <c r="B141" s="7" t="n">
-        <v>569.3586</v>
+        <v>902.692</v>
       </c>
     </row>
     <row r="142" ht="14" customHeight="1">
@@ -1884,7 +1885,7 @@
         </is>
       </c>
       <c r="B143" s="7" t="n">
-        <v>904.9487</v>
+        <v>571.6154</v>
       </c>
     </row>
     <row r="144" ht="14" customHeight="1">
@@ -2051,4 +2052,148 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>策略</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>购电费(元)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>购电量(kWh)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>光伏消纳率</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>峰段购电占比</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>弃光量(kWh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>无储能</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>48052.05</v>
+      </c>
+      <c r="C2" t="n">
+        <v>61789.94</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>88.7%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>30.1%</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>6247.96</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>规则谷充峰放</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>52695.81</v>
+      </c>
+      <c r="C3" t="n">
+        <v>76166.78999999999</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>76.4%</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>21.6%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>13106.48</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>优化模型</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>35126.95</v>
+      </c>
+      <c r="C4" t="n">
+        <v>59482.7</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>13.1%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>相比无储能节省(元)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12925.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>相比规则型节省(元)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>17568.86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/result1.xlsx
+++ b/result1.xlsx
@@ -8,7 +8,6 @@
   <sheets>
     <sheet name="计划购电量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="充放电量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="对照实验" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1865,7 +1864,7 @@
         </is>
       </c>
       <c r="B141" s="7" t="n">
-        <v>902.692</v>
+        <v>569.3586</v>
       </c>
     </row>
     <row r="142" ht="14" customHeight="1">
@@ -1885,7 +1884,7 @@
         </is>
       </c>
       <c r="B143" s="7" t="n">
-        <v>571.6154</v>
+        <v>904.9487</v>
       </c>
     </row>
     <row r="144" ht="14" customHeight="1">
@@ -2052,148 +2051,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>策略</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>购电费(元)</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>购电量(kWh)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>光伏消纳率</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>峰段购电占比</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>弃光量(kWh)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>无储能</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>48052.05</v>
-      </c>
-      <c r="C2" t="n">
-        <v>61789.94</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>88.7%</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>30.1%</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>6247.96</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>规则谷充峰放</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>52695.81</v>
-      </c>
-      <c r="C3" t="n">
-        <v>76166.78999999999</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>76.4%</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>21.6%</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>13106.48</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>优化模型</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>35126.95</v>
-      </c>
-      <c r="C4" t="n">
-        <v>59482.7</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>13.1%</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>相比无储能节省(元)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>12925.1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>相比规则型节省(元)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>17568.86</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/result1.xlsx
+++ b/result1.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="计划购电量" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="充放电量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计划购电量" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="充放电量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对照实验" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1864,7 +1865,7 @@
         </is>
       </c>
       <c r="B141" s="7" t="n">
-        <v>569.3586</v>
+        <v>902.692</v>
       </c>
     </row>
     <row r="142" ht="14" customHeight="1">
@@ -1884,7 +1885,7 @@
         </is>
       </c>
       <c r="B143" s="7" t="n">
-        <v>904.9487</v>
+        <v>571.6154</v>
       </c>
     </row>
     <row r="144" ht="14" customHeight="1">
@@ -2051,4 +2052,148 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>策略</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>购电费(元)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>购电量(kWh)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>光伏消纳率</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>峰段购电占比</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>弃光量(kWh)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>无储能</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>48052.05</v>
+      </c>
+      <c r="C2" t="n">
+        <v>61789.94</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>88.7%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>30.1%</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>6247.96</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>规则谷充峰放</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>52695.81</v>
+      </c>
+      <c r="C3" t="n">
+        <v>76166.78999999999</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>76.4%</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>21.6%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>13106.48</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>优化模型</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>35126.95</v>
+      </c>
+      <c r="C4" t="n">
+        <v>59482.7</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>13.1%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>相比无储能节省(元)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>12925.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>相比规则型节省(元)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>17568.86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>